--- a/IT23588578.xlsx
+++ b/IT23588578.xlsx
@@ -528,7 +528,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>

--- a/IT23588578.xlsx
+++ b/IT23588578.xlsx
@@ -584,7 +584,7 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
